--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,297 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129893765</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97657</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Krakbrändan cypresslummer, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>496376</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6692896</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129893867</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90981</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Krakbrändan tall 3, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>496456</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6692808</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129893727</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97651</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Krakbrändan revlummer, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496489</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6692834</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97657</v>
+        <v>97667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>129893867</v>
       </c>
       <c r="B6" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>129893867</v>
       </c>
       <c r="B6" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>129893867</v>
       </c>
       <c r="B6" t="n">
-        <v>90987</v>
+        <v>90988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>129893867</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>91005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>129893867</v>
       </c>
       <c r="B6" t="n">
-        <v>91021</v>
+        <v>91023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>129893867</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>91110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>129893765</v>
       </c>
       <c r="B5" t="n">
-        <v>97797</v>
+        <v>97710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>129893867</v>
       </c>
       <c r="B6" t="n">
-        <v>91110</v>
+        <v>91023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>129893727</v>
       </c>
       <c r="B7" t="n">
-        <v>97791</v>
+        <v>97704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55406-2025 artfynd.xlsx
+++ b/artfynd/A 55406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65198065</v>
+        <v>129893867</v>
       </c>
       <c r="B2" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223621</v>
+        <v>5685</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skansen, Dlr</t>
+          <t>Krakbrändan tall 3, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496491.0304030611</v>
+        <v>496456</v>
       </c>
       <c r="R2" t="n">
-        <v>6693147.820348199</v>
+        <v>6692808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-04-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-04-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,67 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gallrat</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Stig-Åke Svenson, Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65355765</v>
+        <v>65355759</v>
       </c>
       <c r="B3" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223621</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -856,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496499.9158443807</v>
+        <v>496485</v>
       </c>
       <c r="R3" t="n">
-        <v>6693115.17015865</v>
+        <v>6692707</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,19 +840,9 @@
           <t>2017-04-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-04-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65355761</v>
+        <v>129893765</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,37 +884,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bastberget, Dlr</t>
+          <t>Krakbrändan cypresslummer, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496721.2009482344</v>
+        <v>496376</v>
       </c>
       <c r="R4" t="n">
-        <v>6692945.816191345</v>
+        <v>6692896</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-04-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-04-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,26 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893765</v>
+        <v>129893727</v>
       </c>
       <c r="B5" t="n">
-        <v>97710</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,16 +981,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,17 +1001,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krakbrändan cypresslummer, Dlr</t>
+          <t>Krakbrändan revlummer, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496376</v>
+        <v>496489</v>
       </c>
       <c r="R5" t="n">
-        <v>6692896</v>
+        <v>6692834</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893867</v>
+        <v>65355761</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,37 +1078,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5685</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krakbrändan tall 3, Dlr</t>
+          <t>Bastberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496456</v>
+        <v>496721</v>
       </c>
       <c r="R6" t="n">
-        <v>6692808</v>
+        <v>6692946</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,12 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2017-04-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2017-04-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1152,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893727</v>
+        <v>65198065</v>
       </c>
       <c r="B7" t="n">
-        <v>97704</v>
+        <v>99155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,37 +1179,52 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>223621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krakbrändan revlummer, Dlr</t>
+          <t>Skansen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496489</v>
+        <v>496491</v>
       </c>
       <c r="R7" t="n">
-        <v>6692834</v>
+        <v>6693148</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,12 +1248,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2017-04-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2017-04-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,19 +1264,134 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>gallrat</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Janolof Hermansson, Stig-Åke Svenson, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>65355765</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Krakbrändan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496500</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6693115</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-04-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-04-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
